--- a/docs/downloads/04/tbl_class_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_avaradrano.xlsx
@@ -486,14 +486,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>7.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -555,7 +549,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
@@ -578,14 +572,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>28.6</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -601,14 +595,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>71.40000000000001</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -624,14 +612,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>7.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +635,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>38</v>
-      </c>
-      <c r="E13">
-        <v>92.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -716,14 +698,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -785,7 +761,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D19">
@@ -854,14 +830,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D22">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E22">
-        <v>17.4</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="23">
@@ -872,19 +848,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>1.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="24">
@@ -900,14 +876,8 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>21</v>
-      </c>
-      <c r="E24">
-        <v>53.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -923,14 +893,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D25">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E25">
-        <v>43.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +911,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>2.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -969,14 +933,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D27">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="E27">
-        <v>12.9</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="28">
@@ -992,14 +956,8 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>185</v>
-      </c>
-      <c r="E28">
-        <v>85.3</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +973,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E29">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
